--- a/CO2_Ziwschenspeicherung_Salzkavernen/Kavernenrechner/1_auslegung/CO2_Kaverne_berechnet.xlsx
+++ b/CO2_Ziwschenspeicherung_Salzkavernen/Kavernenrechner/1_auslegung/CO2_Kaverne_berechnet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Annahmen &amp; Ergebnisse" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Gassäule" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Teufenprofile" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Arbeitsgas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Annahmen &amp; Ergebnisse" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gassäule" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teufenprofile" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arbeitsgas" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>102.69</v>
+        <v>102.42</v>
       </c>
     </row>
     <row r="32">
@@ -928,7 +928,7 @@
         <v>921.4</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>112.13</v>
+        <v>112.11</v>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>916.4</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>116.65</v>
+        <v>116.62</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>911.5</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>121.14</v>
+        <v>121.11</v>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
@@ -982,10 +982,10 @@
         <v>16</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>906.7</v>
+        <v>906.6</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>125.61</v>
+        <v>125.57</v>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>901.8</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>130.06</v>
+        <v>130</v>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>897</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>134.48</v>
+        <v>134.41</v>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
@@ -1039,10 +1039,10 @@
         <v>20.5</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>892.3</v>
+        <v>892.2</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>138.88</v>
+        <v>138.8</v>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>887.5</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>143.26</v>
+        <v>143.17</v>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
@@ -1077,10 +1077,10 @@
         <v>23.5</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>882.9</v>
+        <v>882.8</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>147.61</v>
+        <v>147.51</v>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
@@ -1096,10 +1096,10 @@
         <v>25</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>878.2</v>
+        <v>878.1</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>151.94</v>
+        <v>151.83</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
         <v>26.5</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>873.6</v>
+        <v>873.5</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>156.25</v>
+        <v>156.12</v>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         <v>28</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>869</v>
+        <v>868.9</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>160.54</v>
+        <v>160.4</v>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
         <v>29.5</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>864.5</v>
+        <v>864.3</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>164.8</v>
+        <v>164.65</v>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
@@ -1172,10 +1172,10 @@
         <v>31</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>860</v>
+        <v>859.9</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>169.04</v>
+        <v>168.88</v>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         <v>32.5</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>855.6</v>
+        <v>855.4</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>173.26</v>
+        <v>173.08</v>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
         <v>34</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>851.2</v>
+        <v>851</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>177.45</v>
+        <v>177.27</v>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
@@ -1229,10 +1229,10 @@
         <v>35.5</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>846.8</v>
+        <v>846.6</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>181.63</v>
+        <v>181.43</v>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
@@ -1248,10 +1248,10 @@
         <v>37</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>842.5</v>
+        <v>842.3</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>185.78</v>
+        <v>185.58</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
         <v>38.5</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>838.3</v>
+        <v>838.1</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>189.91</v>
+        <v>189.7</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
         <v>40</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>834.1</v>
+        <v>833.9</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>194.03</v>
+        <v>193.8</v>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
@@ -1305,10 +1305,10 @@
         <v>41.5</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>830</v>
+        <v>829.7</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>198.12</v>
+        <v>197.88</v>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
@@ -1324,10 +1324,10 @@
         <v>43</v>
       </c>
       <c r="C26" s="9" t="n">
-        <v>825.9</v>
+        <v>825.6</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>202.19</v>
+        <v>201.94</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         <v>44.5</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>821.9</v>
+        <v>821.6</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>206.24</v>
+        <v>205.98</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
@@ -1362,10 +1362,10 @@
         <v>46</v>
       </c>
       <c r="C28" s="9" t="n">
-        <v>817.9</v>
+        <v>817.6</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>210.27</v>
+        <v>210</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
@@ -1454,22 +1454,22 @@
         <v>10</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>107.8</v>
+        <v>107.6</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>926.5</v>
+        <v>926.3</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>74.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>897.3</v>
+        <v>897</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>43.1</v>
+        <v>45</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>123.9</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5">
@@ -1480,22 +1480,22 @@
         <v>11.5</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>112.4</v>
+        <v>112.1</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>921.5</v>
+        <v>921.4</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>78.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>891.6</v>
+        <v>891.3</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>47.3</v>
+        <v>46.7</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>850.8</v>
+        <v>141.8</v>
       </c>
     </row>
     <row r="6">
@@ -1506,22 +1506,22 @@
         <v>13</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>116.9</v>
+        <v>116.6</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>916.6</v>
+        <v>916.4</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>82.8</v>
+        <v>82.5</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>885.9</v>
+        <v>885.6</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>146.5</v>
+        <v>149.8</v>
       </c>
     </row>
     <row r="7">
@@ -1532,22 +1532,22 @@
         <v>14.5</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>121.3</v>
+        <v>121.1</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>911.7</v>
+        <v>911.5</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>87.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>880.2</v>
+        <v>879.9</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>48.7</v>
+        <v>50.3</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>146.9</v>
+        <v>825.5</v>
       </c>
     </row>
     <row r="8">
@@ -1558,22 +1558,22 @@
         <v>16</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>125.8</v>
+        <v>125.6</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>906.8</v>
+        <v>906.7</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>91.40000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>874.5</v>
+        <v>874.2</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>52.7</v>
+        <v>52.1</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>813.9</v>
+        <v>166.7</v>
       </c>
     </row>
     <row r="9">
@@ -1584,22 +1584,22 @@
         <v>17.5</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>130.2</v>
+        <v>130</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>902</v>
+        <v>901.8</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>95.59999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>868.9</v>
+        <v>868.6</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>53.6</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>172.2</v>
+        <v>172.4</v>
       </c>
     </row>
     <row r="10">
@@ -1610,22 +1610,22 @@
         <v>19</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>134.6</v>
+        <v>134.4</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>897.1</v>
+        <v>897</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>99.90000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>863.3</v>
+        <v>863</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>54.4</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>172.5</v>
+        <v>172.6</v>
       </c>
     </row>
     <row r="11">
@@ -1636,22 +1636,22 @@
         <v>20.5</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>139</v>
+        <v>138.8</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>892.4</v>
+        <v>892.2</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>104.1</v>
+        <v>103.9</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>857.7</v>
+        <v>857.4</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>55.3</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>172.8</v>
+        <v>172.9</v>
       </c>
     </row>
     <row r="12">
@@ -1662,22 +1662,22 @@
         <v>22</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>143.3</v>
+        <v>143.2</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>887.6</v>
+        <v>887.5</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>108.3</v>
+        <v>108.1</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>852.1</v>
+        <v>851.9</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>56.1</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>173.2</v>
+        <v>173.3</v>
       </c>
     </row>
     <row r="13">
@@ -1688,22 +1688,22 @@
         <v>23.5</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>147.7</v>
+        <v>147.5</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>882.9</v>
+        <v>882.8</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>112.4</v>
+        <v>112.2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>846.6</v>
+        <v>846.4</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>57</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>173.6</v>
+        <v>173.7</v>
       </c>
     </row>
     <row r="14">
@@ -1714,22 +1714,22 @@
         <v>25</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>152</v>
+        <v>151.8</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>878.2</v>
+        <v>878.1</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>116.5</v>
+        <v>116.4</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>841.2</v>
+        <v>841</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>57.8</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>174</v>
+        <v>174.1</v>
       </c>
     </row>
     <row r="15">
@@ -1740,22 +1740,22 @@
         <v>26.5</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>156.3</v>
+        <v>156.1</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>873.6</v>
+        <v>873.5</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>120.6</v>
+        <v>120.5</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>835.8</v>
+        <v>835.6</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>58.7</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>174.4</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="16">
@@ -1766,16 +1766,16 @@
         <v>28</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>160.5</v>
+        <v>160.4</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>869</v>
+        <v>868.9</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>124.7</v>
+        <v>124.6</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>830.4</v>
+        <v>830.3</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>59.5</v>
@@ -1792,22 +1792,22 @@
         <v>29.5</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>164.8</v>
+        <v>164.7</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>864.5</v>
+        <v>864.4</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>128.8</v>
+        <v>128.6</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>825.1</v>
+        <v>825</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>60.4</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>175.3</v>
+        <v>175.4</v>
       </c>
     </row>
     <row r="18">
@@ -1818,19 +1818,19 @@
         <v>31</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>169</v>
+        <v>168.9</v>
       </c>
       <c r="D18" s="9" t="n">
         <v>859.9</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>132.8</v>
+        <v>132.7</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>819.9</v>
+        <v>819.7</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>61.2</v>
+        <v>61.3</v>
       </c>
       <c r="H18" s="9" t="n">
         <v>175.8</v>
@@ -1844,16 +1844,16 @@
         <v>32.5</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>173.2</v>
+        <v>173.1</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>855.5</v>
+        <v>855.4</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>136.8</v>
+        <v>136.7</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>814.7</v>
+        <v>814.6</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>62.1</v>
@@ -1870,22 +1870,22 @@
         <v>34</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>177.4</v>
+        <v>177.3</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>851.1</v>
+        <v>851</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>140.7</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>809.6</v>
+        <v>809.5</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>176.7</v>
+        <v>176.8</v>
       </c>
     </row>
     <row r="21">
@@ -1896,22 +1896,22 @@
         <v>35.5</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>181.5</v>
+        <v>181.4</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>846.7</v>
+        <v>846.6</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>144.7</v>
+        <v>144.6</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>804.5</v>
+        <v>804.4</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>63.8</v>
+        <v>63.9</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>177.2</v>
+        <v>177.3</v>
       </c>
     </row>
     <row r="22">
@@ -1925,19 +1925,19 @@
         <v>185.6</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>842.4</v>
+        <v>842.3</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>148.6</v>
+        <v>148.5</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>799.6</v>
+        <v>799.5</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>64.7</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>177.7</v>
+        <v>177.8</v>
       </c>
     </row>
     <row r="23">
@@ -1957,13 +1957,13 @@
         <v>152.5</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>794.7</v>
+        <v>794.6</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>65.59999999999999</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>178.2</v>
+        <v>178.3</v>
       </c>
     </row>
     <row r="24">
@@ -1980,7 +1980,7 @@
         <v>833.9</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>156.4</v>
+        <v>156.3</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>789.8</v>
@@ -1989,7 +1989,7 @@
         <v>66.5</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>178.7</v>
+        <v>178.8</v>
       </c>
     </row>
     <row r="25">
@@ -2003,16 +2003,16 @@
         <v>197.9</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>829.8</v>
+        <v>829.7</v>
       </c>
       <c r="E25" s="9" t="n">
         <v>160.2</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>785.1</v>
+        <v>785</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>67.3</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="H25" s="9" t="n">
         <v>179.2</v>
@@ -2026,13 +2026,13 @@
         <v>43</v>
       </c>
       <c r="C26" s="9" t="n">
-        <v>202</v>
+        <v>201.9</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>825.7</v>
+        <v>825.6</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>164.1</v>
+        <v>164</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>780.4</v>
